--- a/experiments/spatial_graph/experiment_metrics.xlsx
+++ b/experiments/spatial_graph/experiment_metrics.xlsx
@@ -24,13 +24,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -442,77 +454,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -567,19 +579,19 @@
           <t>0.759±0.068</t>
         </is>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="2" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -632,19 +644,19 @@
           <t>0.692±0.044</t>
         </is>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.6008</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="2" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>0.2955</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.5419</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.6897</v>
       </c>
     </row>
@@ -697,19 +709,19 @@
           <t>0.753±0.051</t>
         </is>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -762,19 +774,19 @@
           <t>0.694±0.067</t>
         </is>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.629</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <v>0.8879</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>0.4015</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.5659</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.6913</v>
       </c>
     </row>
@@ -827,19 +839,19 @@
           <t>0.748±0.096</t>
         </is>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.6935</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>0.4848</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.6136</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.7397</v>
       </c>
     </row>
@@ -892,19 +904,19 @@
           <t>0.678±0.057</t>
         </is>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.5726</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="2" t="n">
         <v>0.9397</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.524</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.6728</v>
       </c>
     </row>
@@ -955,152 +967,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1130,10 +1142,10 @@
       <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>0.7103</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.1252</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -1146,10 +1158,10 @@
           <t>[0.601, 0.820]</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>0.9433</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>0.08790000000000001</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -1162,10 +1174,10 @@
           <t>[0.866, 1.020]</t>
         </is>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.4929</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.2954</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -1178,10 +1190,10 @@
           <t>[0.234, 0.752]</t>
         </is>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="R2" s="2" t="n">
         <v>0.6464</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="S2" s="2" t="n">
         <v>0.1057</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -1194,10 +1206,10 @@
           <t>[0.554, 0.739]</t>
         </is>
       </c>
-      <c r="V2" s="1" t="n">
+      <c r="V2" s="2" t="n">
         <v>0.7593</v>
       </c>
-      <c r="W2" s="1" t="n">
+      <c r="W2" s="2" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -1210,19 +1222,19 @@
           <t>[0.700, 0.819]</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="n">
+      <c r="Z2" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA2" s="1" t="n">
+      <c r="AA2" s="2" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB2" s="1" t="n">
+      <c r="AB2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC2" s="1" t="n">
+      <c r="AC2" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="AD2" s="1" t="n">
+      <c r="AD2" s="2" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -1250,10 +1262,10 @@
       <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>0.6002999999999999</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.0872</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -1266,10 +1278,10 @@
           <t>[0.524, 0.677]</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.06850000000000001</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -1282,10 +1294,10 @@
           <t>[0.890, 1.010]</t>
         </is>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.2976</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.2183</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -1298,10 +1310,10 @@
           <t>[0.106, 0.489]</t>
         </is>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.5523</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="S3" s="2" t="n">
         <v>0.08450000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -1314,10 +1326,10 @@
           <t>[0.478, 0.626]</t>
         </is>
       </c>
-      <c r="V3" s="1" t="n">
+      <c r="V3" s="2" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="W3" s="2" t="n">
         <v>0.0439</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -1330,19 +1342,19 @@
           <t>[0.653, 0.731]</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="n">
+      <c r="Z3" s="2" t="n">
         <v>0.6008</v>
       </c>
-      <c r="AA3" s="1" t="n">
+      <c r="AA3" s="2" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB3" s="1" t="n">
+      <c r="AB3" s="2" t="n">
         <v>0.2955</v>
       </c>
-      <c r="AC3" s="1" t="n">
+      <c r="AC3" s="2" t="n">
         <v>0.5419</v>
       </c>
-      <c r="AD3" s="1" t="n">
+      <c r="AD3" s="2" t="n">
         <v>0.6897</v>
       </c>
     </row>
@@ -1370,10 +1382,10 @@
       <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.7077</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.0814</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -1386,10 +1398,10 @@
           <t>[0.636, 0.779]</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>0.9467</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.0767</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -1402,10 +1414,10 @@
           <t>[0.879, 1.014]</t>
         </is>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.4905</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.201</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -1418,10 +1430,10 @@
           <t>[0.314, 0.667]</t>
         </is>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>0.6311</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.0733</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -1434,10 +1446,10 @@
           <t>[0.567, 0.695]</t>
         </is>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="V4" s="2" t="n">
         <v>0.7534999999999999</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="W4" s="2" t="n">
         <v>0.0514</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -1450,19 +1462,19 @@
           <t>[0.708, 0.799]</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="Z4" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AA4" s="2" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AB4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AC4" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AD4" s="2" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -1490,10 +1502,10 @@
       <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>0.626</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.1265</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -1506,10 +1518,10 @@
           <t>[0.515, 0.737]</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>0.89</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.1114</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -1522,10 +1534,10 @@
           <t>[0.792, 0.988]</t>
         </is>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.3929</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.3051</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -1538,10 +1550,10 @@
           <t>[0.125, 0.660]</t>
         </is>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <v>0.584</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="S5" s="2" t="n">
         <v>0.1059</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -1554,10 +1566,10 @@
           <t>[0.491, 0.677]</t>
         </is>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="V5" s="2" t="n">
         <v>0.6944</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="W5" s="2" t="n">
         <v>0.0675</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -1570,19 +1582,19 @@
           <t>[0.635, 0.754]</t>
         </is>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0.629</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AA5" s="2" t="n">
         <v>0.8879</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AB5" s="2" t="n">
         <v>0.4015</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AC5" s="2" t="n">
         <v>0.5659</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AD5" s="2" t="n">
         <v>0.6913</v>
       </c>
     </row>
@@ -1610,10 +1622,10 @@
       <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.6962</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.1528</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -1626,10 +1638,10 @@
           <t>[0.562, 0.830]</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>0.93</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.0711</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -1642,10 +1654,10 @@
           <t>[0.868, 0.992]</t>
         </is>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.4929</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.2906</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -1658,10 +1670,10 @@
           <t>[0.238, 0.748]</t>
         </is>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="2" t="n">
         <v>0.6348</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="S6" s="2" t="n">
         <v>0.1239</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -1674,10 +1686,10 @@
           <t>[0.526, 0.743]</t>
         </is>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="V6" s="2" t="n">
         <v>0.7481</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="W6" s="2" t="n">
         <v>0.0958</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -1690,19 +1702,19 @@
           <t>[0.664, 0.832]</t>
         </is>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="Z6" s="2" t="n">
         <v>0.6935</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AA6" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AB6" s="2" t="n">
         <v>0.4848</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AC6" s="2" t="n">
         <v>0.6136</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AD6" s="2" t="n">
         <v>0.7397</v>
       </c>
     </row>
@@ -1730,10 +1742,10 @@
       <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>0.5731000000000001</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.1165</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -1746,10 +1758,10 @@
           <t>[0.471, 0.675]</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>0.9417</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.08119999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -1762,10 +1774,10 @@
           <t>[0.870, 1.013]</t>
         </is>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.2548</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.2852</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -1778,10 +1790,10 @@
           <t>[0.005, 0.505]</t>
         </is>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7" s="2" t="n">
         <v>0.5414</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="S7" s="2" t="n">
         <v>0.1059</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -1794,10 +1806,10 @@
           <t>[0.449, 0.634]</t>
         </is>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="V7" s="2" t="n">
         <v>0.6778999999999999</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="W7" s="2" t="n">
         <v>0.0566</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -1810,19 +1822,19 @@
           <t>[0.628, 0.727]</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="Z7" s="2" t="n">
         <v>0.5726</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AA7" s="2" t="n">
         <v>0.9397</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AB7" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AC7" s="2" t="n">
         <v>0.524</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AD7" s="2" t="n">
         <v>0.6728</v>
       </c>
     </row>
@@ -1858,77 +1870,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1983,19 +1995,19 @@
           <t>0.794±0.057</t>
         </is>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>0.7823</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="2" t="n">
         <v>0.8966</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>0.6818</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.7123</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.7939000000000001</v>
       </c>
     </row>
@@ -2048,19 +2060,19 @@
           <t>0.722±0.051</t>
         </is>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.6532</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>0.4091</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.5806</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.7151999999999999</v>
       </c>
     </row>
@@ -2113,19 +2125,19 @@
           <t>0.807±0.075</t>
         </is>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.7661</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>0.5606</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.6667</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2178,19 +2190,19 @@
           <t>0.693±0.058</t>
         </is>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.6089</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <v>0.9569</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>0.303</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.5468</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.6959</v>
       </c>
     </row>
@@ -2243,19 +2255,19 @@
           <t>0.804±0.081</t>
         </is>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.7823</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>0.6515</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.7013</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2308,19 +2320,19 @@
           <t>0.721±0.071</t>
         </is>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.6492</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="2" t="n">
         <v>0.9397</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>0.3939</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.5767</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.7148</v>
       </c>
     </row>
@@ -2371,152 +2383,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -2546,10 +2558,10 @@
       <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>0.7821</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.07530000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -2562,10 +2574,10 @@
           <t>[0.735, 0.829]</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>0.8917</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>0.1245</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -2578,10 +2590,10 @@
           <t>[0.814, 0.969]</t>
         </is>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.675</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.2011</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -2594,10 +2606,10 @@
           <t>[0.550, 0.800]</t>
         </is>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="R2" s="2" t="n">
         <v>0.738</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="S2" s="2" t="n">
         <v>0.1246</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -2610,10 +2622,10 @@
           <t>[0.661, 0.815]</t>
         </is>
       </c>
-      <c r="V2" s="1" t="n">
+      <c r="V2" s="2" t="n">
         <v>0.794</v>
       </c>
-      <c r="W2" s="1" t="n">
+      <c r="W2" s="2" t="n">
         <v>0.057</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -2626,19 +2638,19 @@
           <t>[0.759, 0.829]</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="n">
+      <c r="Z2" s="2" t="n">
         <v>0.7823</v>
       </c>
-      <c r="AA2" s="1" t="n">
+      <c r="AA2" s="2" t="n">
         <v>0.8966</v>
       </c>
-      <c r="AB2" s="1" t="n">
+      <c r="AB2" s="2" t="n">
         <v>0.6818</v>
       </c>
-      <c r="AC2" s="1" t="n">
+      <c r="AC2" s="2" t="n">
         <v>0.7123</v>
       </c>
-      <c r="AD2" s="1" t="n">
+      <c r="AD2" s="2" t="n">
         <v>0.7939000000000001</v>
       </c>
     </row>
@@ -2666,10 +2678,10 @@
       <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>0.6542</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.104</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -2682,10 +2694,10 @@
           <t>[0.590, 0.719]</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>0.9292</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.07870000000000001</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -2698,10 +2710,10 @@
           <t>[0.880, 0.978]</t>
         </is>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.3979</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.2374</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -2714,10 +2726,10 @@
           <t>[0.251, 0.545]</t>
         </is>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.5999</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="S3" s="2" t="n">
         <v>0.0867</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -2730,10 +2742,10 @@
           <t>[0.546, 0.654]</t>
         </is>
       </c>
-      <c r="V3" s="1" t="n">
+      <c r="V3" s="2" t="n">
         <v>0.7223000000000001</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="W3" s="2" t="n">
         <v>0.0507</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -2746,19 +2758,19 @@
           <t>[0.691, 0.754]</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="n">
+      <c r="Z3" s="2" t="n">
         <v>0.6532</v>
       </c>
-      <c r="AA3" s="1" t="n">
+      <c r="AA3" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB3" s="1" t="n">
+      <c r="AB3" s="2" t="n">
         <v>0.4091</v>
       </c>
-      <c r="AC3" s="1" t="n">
+      <c r="AC3" s="2" t="n">
         <v>0.5806</v>
       </c>
-      <c r="AD3" s="1" t="n">
+      <c r="AD3" s="2" t="n">
         <v>0.7151999999999999</v>
       </c>
     </row>
@@ -2786,10 +2798,10 @@
       <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.7619</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.1304</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -2802,10 +2814,10 @@
           <t>[0.681, 0.843]</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -2818,10 +2830,10 @@
           <t>[1.000, 1.000]</t>
         </is>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.5375</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.2725</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -2834,10 +2846,10 @@
           <t>[0.369, 0.706]</t>
         </is>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>0.6819</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.104</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -2850,10 +2862,10 @@
           <t>[0.617, 0.746]</t>
         </is>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="V4" s="2" t="n">
         <v>0.8067</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="W4" s="2" t="n">
         <v>0.07539999999999999</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -2866,19 +2878,19 @@
           <t>[0.760, 0.853]</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="Z4" s="2" t="n">
         <v>0.7661</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AB4" s="2" t="n">
         <v>0.5606</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AC4" s="2" t="n">
         <v>0.6667</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AD4" s="2" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2906,10 +2918,10 @@
       <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>0.6071</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.097</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -2922,10 +2934,10 @@
           <t>[0.547, 0.667]</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>0.9458</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.1179</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -2938,10 +2950,10 @@
           <t>[0.873, 1.019]</t>
         </is>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.2771</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.2661</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -2954,10 +2966,10 @@
           <t>[0.112, 0.442]</t>
         </is>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <v>0.5527</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="S5" s="2" t="n">
         <v>0.0575</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -2970,10 +2982,10 @@
           <t>[0.517, 0.588]</t>
         </is>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="V5" s="2" t="n">
         <v>0.6931</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="W5" s="2" t="n">
         <v>0.0583</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -2986,19 +2998,19 @@
           <t>[0.657, 0.729]</t>
         </is>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0.6089</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AA5" s="2" t="n">
         <v>0.9569</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AB5" s="2" t="n">
         <v>0.303</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AC5" s="2" t="n">
         <v>0.5468</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AD5" s="2" t="n">
         <v>0.6959</v>
       </c>
     </row>
@@ -3026,10 +3038,10 @@
       <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.7798</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.1058</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -3042,10 +3054,10 @@
           <t>[0.714, 0.845]</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>0.9333</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.0861</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -3058,10 +3070,10 @@
           <t>[0.880, 0.987]</t>
         </is>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.6417</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.2486</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -3074,10 +3086,10 @@
           <t>[0.488, 0.796]</t>
         </is>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="2" t="n">
         <v>0.7307</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="S6" s="2" t="n">
         <v>0.164</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -3090,10 +3102,10 @@
           <t>[0.629, 0.832]</t>
         </is>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="V6" s="2" t="n">
         <v>0.8043</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="W6" s="2" t="n">
         <v>0.08069999999999999</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -3106,19 +3118,19 @@
           <t>[0.754, 0.854]</t>
         </is>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="Z6" s="2" t="n">
         <v>0.7823</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AA6" s="2" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AB6" s="2" t="n">
         <v>0.6515</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AC6" s="2" t="n">
         <v>0.7013</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AD6" s="2" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -3146,10 +3158,10 @@
       <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>0.6512</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.1175</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -3162,10 +3174,10 @@
           <t>[0.578, 0.724]</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>0.9417</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.1115</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -3178,10 +3190,10 @@
           <t>[0.873, 1.011]</t>
         </is>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.4021</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.2927</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -3194,10 +3206,10 @@
           <t>[0.221, 0.583]</t>
         </is>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7" s="2" t="n">
         <v>0.6137</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="S7" s="2" t="n">
         <v>0.1667</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -3210,10 +3222,10 @@
           <t>[0.510, 0.717]</t>
         </is>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="V7" s="2" t="n">
         <v>0.7208</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="W7" s="2" t="n">
         <v>0.0708</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -3226,19 +3238,19 @@
           <t>[0.677, 0.765]</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="Z7" s="2" t="n">
         <v>0.6492</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AA7" s="2" t="n">
         <v>0.9397</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AB7" s="2" t="n">
         <v>0.3939</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AC7" s="2" t="n">
         <v>0.5767</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AD7" s="2" t="n">
         <v>0.7148</v>
       </c>
     </row>
@@ -3274,77 +3286,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3399,19 +3411,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>0.4545</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.617</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -3464,19 +3476,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.6573</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="L3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>0.3561</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.5770999999999999</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.7319</v>
       </c>
     </row>
@@ -3529,19 +3541,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.7419</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="L4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>0.5152</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.6444</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.7838000000000001</v>
       </c>
     </row>
@@ -3594,19 +3606,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.6935</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="L5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>0.4242</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.6042</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.7532</v>
       </c>
     </row>
@@ -3659,19 +3671,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="L6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>0.4545</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.617</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -3724,19 +3736,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.6452</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="L7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>0.3333</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.5686</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.725</v>
       </c>
     </row>
@@ -3787,152 +3799,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3962,10 +3974,10 @@
       <c r="E2" t="n">
         <v>62</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.4104</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -3978,10 +3990,10 @@
           <t>[0.608, 0.812]</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -3994,10 +4006,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.2419</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.3813</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -4010,10 +4022,10 @@
           <t>[0.147, 0.337]</t>
         </is>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="R2" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="S2" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -4026,10 +4038,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V2" s="1" t="n">
+      <c r="V2" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W2" s="1" t="n">
+      <c r="W2" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -4042,19 +4054,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="n">
+      <c r="Z2" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA2" s="1" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="1" t="n">
+      <c r="AB2" s="2" t="n">
         <v>0.4545</v>
       </c>
-      <c r="AC2" s="1" t="n">
+      <c r="AC2" s="2" t="n">
         <v>0.617</v>
       </c>
-      <c r="AD2" s="1" t="n">
+      <c r="AD2" s="2" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -4082,10 +4094,10 @@
       <c r="E3" t="n">
         <v>62</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>0.6573</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.4347</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -4098,10 +4110,10 @@
           <t>[0.549, 0.765]</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="K3" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -4114,10 +4126,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>0.1895</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>0.3408</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -4130,10 +4142,10 @@
           <t>[0.105, 0.274]</t>
         </is>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S3" s="1" t="n">
+      <c r="S3" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -4146,10 +4158,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V3" s="1" t="n">
+      <c r="V3" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W3" s="1" t="n">
+      <c r="W3" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -4162,19 +4174,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="n">
+      <c r="Z3" s="2" t="n">
         <v>0.6573</v>
       </c>
-      <c r="AA3" s="1" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" s="1" t="n">
+      <c r="AB3" s="2" t="n">
         <v>0.3561</v>
       </c>
-      <c r="AC3" s="1" t="n">
+      <c r="AC3" s="2" t="n">
         <v>0.5770999999999999</v>
       </c>
-      <c r="AD3" s="1" t="n">
+      <c r="AD3" s="2" t="n">
         <v>0.7319</v>
       </c>
     </row>
@@ -4202,10 +4214,10 @@
       <c r="E4" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.7419</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.4023</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -4218,10 +4230,10 @@
           <t>[0.642, 0.842]</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="K4" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -4234,10 +4246,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>0.2742</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>0.4117</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -4250,10 +4262,10 @@
           <t>[0.172, 0.377]</t>
         </is>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="S4" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -4266,10 +4278,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="V4" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="W4" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -4282,19 +4294,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="Z4" s="2" t="n">
         <v>0.7419</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AB4" s="2" t="n">
         <v>0.5152</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AC4" s="2" t="n">
         <v>0.6444</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AD4" s="2" t="n">
         <v>0.7838000000000001</v>
       </c>
     </row>
@@ -4322,10 +4334,10 @@
       <c r="E5" t="n">
         <v>62</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>0.6935</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.4281</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -4338,10 +4350,10 @@
           <t>[0.587, 0.800]</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="K5" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -4354,10 +4366,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>0.2258</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>0.3807</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -4370,10 +4382,10 @@
           <t>[0.131, 0.321]</t>
         </is>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="R5" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="S5" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -4386,10 +4398,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="V5" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="W5" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -4402,19 +4414,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="Z5" s="2" t="n">
         <v>0.6935</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AB5" s="2" t="n">
         <v>0.4242</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AC5" s="2" t="n">
         <v>0.6042</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AD5" s="2" t="n">
         <v>0.7532</v>
       </c>
     </row>
@@ -4442,10 +4454,10 @@
       <c r="E6" t="n">
         <v>62</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.4203</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -4458,10 +4470,10 @@
           <t>[0.605, 0.814]</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -4474,10 +4486,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>0.2419</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>0.3919</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -4490,10 +4502,10 @@
           <t>[0.144, 0.339]</t>
         </is>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="R6" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="S6" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -4506,10 +4518,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="V6" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="W6" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -4522,19 +4534,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="Z6" s="2" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AB6" s="2" t="n">
         <v>0.4545</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AC6" s="2" t="n">
         <v>0.617</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AD6" s="2" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -4562,10 +4574,10 @@
       <c r="E7" t="n">
         <v>62</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>0.6452</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.4448</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -4578,10 +4590,10 @@
           <t>[0.534, 0.756]</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -4594,10 +4606,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>0.1774</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>0.3369</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -4610,10 +4622,10 @@
           <t>[0.094, 0.261]</t>
         </is>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="R7" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="S7" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -4626,10 +4638,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="V7" s="2" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="W7" s="2" t="n">
         <v>0.503</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -4642,19 +4654,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="Z7" s="2" t="n">
         <v>0.6452</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AA7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AB7" s="2" t="n">
         <v>0.3333</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AC7" s="2" t="n">
         <v>0.5686</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AD7" s="2" t="n">
         <v>0.725</v>
       </c>
     </row>

--- a/experiments/spatial_graph/experiment_metrics.xlsx
+++ b/experiments/spatial_graph/experiment_metrics.xlsx
@@ -24,16 +24,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -454,77 +442,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -579,19 +567,19 @@
           <t>0.759±0.068</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.625</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -644,19 +632,19 @@
           <t>0.692±0.044</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.6008</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.2955</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.5419</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.6897</v>
       </c>
     </row>
@@ -709,19 +697,19 @@
           <t>0.753±0.051</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.625</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -774,19 +762,19 @@
           <t>0.694±0.067</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.629</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.8879</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.4015</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.5659</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.6913</v>
       </c>
     </row>
@@ -839,19 +827,19 @@
           <t>0.748±0.096</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.4848</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.6136</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.7397</v>
       </c>
     </row>
@@ -904,19 +892,19 @@
           <t>0.678±0.057</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.5726</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.9397</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.524</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.6728</v>
       </c>
     </row>
@@ -967,152 +955,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1142,10 +1130,10 @@
       <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.7103</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.1252</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -1158,10 +1146,10 @@
           <t>[0.601, 0.820]</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.9433</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.08790000000000001</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -1174,10 +1162,10 @@
           <t>[0.866, 1.020]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.4929</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.2954</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -1190,10 +1178,10 @@
           <t>[0.234, 0.752]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0.6464</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.1057</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -1206,10 +1194,10 @@
           <t>[0.554, 0.739]</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.7593</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="1" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -1222,19 +1210,19 @@
           <t>[0.700, 0.819]</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.625</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -1262,10 +1250,10 @@
       <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.6002999999999999</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.0872</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -1278,10 +1266,10 @@
           <t>[0.524, 0.677]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.95</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.06850000000000001</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -1294,10 +1282,10 @@
           <t>[0.890, 1.010]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.2976</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.2183</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -1310,10 +1298,10 @@
           <t>[0.106, 0.489]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.5523</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>0.08450000000000001</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -1326,10 +1314,10 @@
           <t>[0.478, 0.626]</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="1" t="n">
         <v>0.0439</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -1342,19 +1330,19 @@
           <t>[0.653, 0.731]</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.6008</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>0.2955</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.5419</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.6897</v>
       </c>
     </row>
@@ -1382,10 +1370,10 @@
       <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.7077</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.0814</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -1398,10 +1386,10 @@
           <t>[0.636, 0.779]</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.9467</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.0767</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -1414,10 +1402,10 @@
           <t>[0.879, 1.014]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.4905</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.201</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -1430,10 +1418,10 @@
           <t>[0.314, 0.667]</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.6311</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="1" t="n">
         <v>0.0733</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -1446,10 +1434,10 @@
           <t>[0.567, 0.695]</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.7534999999999999</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="1" t="n">
         <v>0.0514</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -1462,19 +1450,19 @@
           <t>[0.708, 0.799]</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="1" t="n">
         <v>0.9483</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.625</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.7534</v>
       </c>
     </row>
@@ -1502,10 +1490,10 @@
       <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.626</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.1265</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -1518,10 +1506,10 @@
           <t>[0.515, 0.737]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.89</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.1114</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -1534,10 +1522,10 @@
           <t>[0.792, 0.988]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.3051</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -1550,10 +1538,10 @@
           <t>[0.125, 0.660]</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.584</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="1" t="n">
         <v>0.1059</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -1566,10 +1554,10 @@
           <t>[0.491, 0.677]</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.6944</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="1" t="n">
         <v>0.0675</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -1582,19 +1570,19 @@
           <t>[0.635, 0.754]</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.629</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="1" t="n">
         <v>0.8879</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0.4015</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.5659</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.6913</v>
       </c>
     </row>
@@ -1622,10 +1610,10 @@
       <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.6962</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.1528</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -1638,10 +1626,10 @@
           <t>[0.562, 0.830]</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.93</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.0711</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -1654,10 +1642,10 @@
           <t>[0.868, 0.992]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.4929</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.2906</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -1670,10 +1658,10 @@
           <t>[0.238, 0.748]</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.6348</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.1239</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -1686,10 +1674,10 @@
           <t>[0.526, 0.743]</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.7481</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.0958</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -1702,19 +1690,19 @@
           <t>[0.664, 0.832]</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="1" t="n">
         <v>0.4848</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.6136</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.7397</v>
       </c>
     </row>
@@ -1742,10 +1730,10 @@
       <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.5731000000000001</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.1165</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -1758,10 +1746,10 @@
           <t>[0.471, 0.675]</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.9417</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.08119999999999999</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -1774,10 +1762,10 @@
           <t>[0.870, 1.013]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.2548</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.2852</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -1790,10 +1778,10 @@
           <t>[0.005, 0.505]</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.5414</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.1059</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -1806,10 +1794,10 @@
           <t>[0.449, 0.634]</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.6778999999999999</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.0566</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -1822,19 +1810,19 @@
           <t>[0.628, 0.727]</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.5726</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="1" t="n">
         <v>0.9397</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.524</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.6728</v>
       </c>
     </row>
@@ -1870,77 +1858,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -1995,19 +1983,19 @@
           <t>0.794±0.057</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.8966</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.6818</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.7123</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.7939000000000001</v>
       </c>
     </row>
@@ -2060,19 +2048,19 @@
           <t>0.722±0.051</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.6532</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.4091</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.5806</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.7151999999999999</v>
       </c>
     </row>
@@ -2125,19 +2113,19 @@
           <t>0.807±0.075</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.7661</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.5606</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.6667</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2190,19 +2178,19 @@
           <t>0.693±0.058</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.6089</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.9569</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.303</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.5468</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.6959</v>
       </c>
     </row>
@@ -2255,19 +2243,19 @@
           <t>0.804±0.081</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.6515</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.7013</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2320,19 +2308,19 @@
           <t>0.721±0.071</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.6492</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.9397</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.3939</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.5767</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.7148</v>
       </c>
     </row>
@@ -2383,152 +2371,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -2558,10 +2546,10 @@
       <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.7821</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.07530000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -2574,10 +2562,10 @@
           <t>[0.735, 0.829]</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.8917</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.1245</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -2590,10 +2578,10 @@
           <t>[0.814, 0.969]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.675</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.2011</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -2606,10 +2594,10 @@
           <t>[0.550, 0.800]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0.738</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.1246</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -2622,10 +2610,10 @@
           <t>[0.661, 0.815]</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.794</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="1" t="n">
         <v>0.057</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -2638,19 +2626,19 @@
           <t>[0.759, 0.829]</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="1" t="n">
         <v>0.8966</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.6818</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.7123</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.7939000000000001</v>
       </c>
     </row>
@@ -2678,10 +2666,10 @@
       <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.6542</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.104</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -2694,10 +2682,10 @@
           <t>[0.590, 0.719]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.9292</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.07870000000000001</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -2710,10 +2698,10 @@
           <t>[0.880, 0.978]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.3979</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.2374</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -2726,10 +2714,10 @@
           <t>[0.251, 0.545]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.5999</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>0.0867</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -2742,10 +2730,10 @@
           <t>[0.546, 0.654]</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.7223000000000001</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="1" t="n">
         <v>0.0507</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -2758,19 +2746,19 @@
           <t>[0.691, 0.754]</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.6532</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>0.4091</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.5806</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.7151999999999999</v>
       </c>
     </row>
@@ -2798,10 +2786,10 @@
       <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.7619</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.1304</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -2814,10 +2802,10 @@
           <t>[0.681, 0.843]</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -2830,10 +2818,10 @@
           <t>[1.000, 1.000]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.5375</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.2725</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -2846,10 +2834,10 @@
           <t>[0.369, 0.706]</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.6819</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="1" t="n">
         <v>0.104</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -2862,10 +2850,10 @@
           <t>[0.617, 0.746]</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.8067</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="1" t="n">
         <v>0.07539999999999999</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -2878,19 +2866,19 @@
           <t>[0.760, 0.853]</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.7661</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="1" t="n">
         <v>0.5606</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.6667</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2918,10 +2906,10 @@
       <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.6071</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.097</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -2934,10 +2922,10 @@
           <t>[0.547, 0.667]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.9458</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.1179</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -2950,10 +2938,10 @@
           <t>[0.873, 1.019]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.2771</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.2661</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -2966,10 +2954,10 @@
           <t>[0.112, 0.442]</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.5527</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="1" t="n">
         <v>0.0575</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -2982,10 +2970,10 @@
           <t>[0.517, 0.588]</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.6931</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="1" t="n">
         <v>0.0583</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -2998,19 +2986,19 @@
           <t>[0.657, 0.729]</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.6089</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="1" t="n">
         <v>0.9569</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0.303</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.5468</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.6959</v>
       </c>
     </row>
@@ -3038,10 +3026,10 @@
       <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.7798</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.1058</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -3054,10 +3042,10 @@
           <t>[0.714, 0.845]</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.9333</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.0861</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -3070,10 +3058,10 @@
           <t>[0.880, 0.987]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.6417</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.2486</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -3086,10 +3074,10 @@
           <t>[0.488, 0.796]</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.7307</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.164</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -3102,10 +3090,10 @@
           <t>[0.629, 0.832]</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.8043</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.08069999999999999</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -3118,19 +3106,19 @@
           <t>[0.754, 0.854]</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.7823</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="1" t="n">
         <v>0.6515</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.7013</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -3158,10 +3146,10 @@
       <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.6512</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.1175</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -3174,10 +3162,10 @@
           <t>[0.578, 0.724]</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.9417</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.1115</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -3190,10 +3178,10 @@
           <t>[0.873, 1.011]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.4021</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.2927</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -3206,10 +3194,10 @@
           <t>[0.221, 0.583]</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.6137</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.1667</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -3222,10 +3210,10 @@
           <t>[0.510, 0.717]</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.7208</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.0708</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -3238,19 +3226,19 @@
           <t>[0.677, 0.765]</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.6492</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="1" t="n">
         <v>0.9397</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.3939</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.5767</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.7148</v>
       </c>
     </row>
@@ -3286,77 +3274,77 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3411,19 +3399,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.4545</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.617</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -3476,19 +3464,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.6573</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.3561</v>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.5770999999999999</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.7319</v>
       </c>
     </row>
@@ -3541,19 +3529,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.5152</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.6444</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.7838000000000001</v>
       </c>
     </row>
@@ -3606,19 +3594,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.4242</v>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.6042</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.7532</v>
       </c>
     </row>
@@ -3671,19 +3659,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.4545</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.617</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -3736,19 +3724,19 @@
           <t>0.468±0.503</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.6452</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.3333</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.5686</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.725</v>
       </c>
     </row>
@@ -3799,152 +3787,152 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MaxTrials</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>N Folds/Subjects</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Acc Mean</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Acc SD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Acc Mean±SD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Acc 95% CI</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sens Mean</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sens SD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sens Mean±SD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sens 95% CI</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Spec Mean</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Spec SD</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Spec Mean±SD</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Spec 95% CI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Prec Mean</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Prec SD</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Prec Mean±SD</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Prec 95% CI</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>F1 SD</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>F1 Mean±SD</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>F1 95% CI</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Overall Acc</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Overall Sens</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Overall Spec</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Overall Prec</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Overall F1</t>
         </is>
@@ -3974,10 +3962,10 @@
       <c r="E2" t="n">
         <v>62</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="1" t="n">
         <v>0.4104</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -3990,10 +3978,10 @@
           <t>[0.608, 0.812]</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L2" t="inlineStr">
@@ -4006,10 +3994,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.2419</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="1" t="n">
         <v>0.3813</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -4022,10 +4010,10 @@
           <t>[0.147, 0.337]</t>
         </is>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T2" t="inlineStr">
@@ -4038,10 +4026,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X2" t="inlineStr">
@@ -4054,19 +4042,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
+      <c r="Z2" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="1" t="n">
         <v>0.4545</v>
       </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.617</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -4094,10 +4082,10 @@
       <c r="E3" t="n">
         <v>62</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="1" t="n">
         <v>0.6573</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="1" t="n">
         <v>0.4347</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -4110,10 +4098,10 @@
           <t>[0.549, 0.765]</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L3" t="inlineStr">
@@ -4126,10 +4114,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.1895</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.3408</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -4142,10 +4130,10 @@
           <t>[0.105, 0.274]</t>
         </is>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T3" t="inlineStr">
@@ -4158,10 +4146,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="W3" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X3" t="inlineStr">
@@ -4174,19 +4162,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="Z3" s="1" t="n">
         <v>0.6573</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="1" t="n">
         <v>0.3561</v>
       </c>
-      <c r="AC3" s="2" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.5770999999999999</v>
       </c>
-      <c r="AD3" s="2" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.7319</v>
       </c>
     </row>
@@ -4214,10 +4202,10 @@
       <c r="E4" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="1" t="n">
         <v>0.4023</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -4230,10 +4218,10 @@
           <t>[0.642, 0.842]</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L4" t="inlineStr">
@@ -4246,10 +4234,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.2742</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.4117</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -4262,10 +4250,10 @@
           <t>[0.172, 0.377]</t>
         </is>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T4" t="inlineStr">
@@ -4278,10 +4266,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="W4" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X4" t="inlineStr">
@@ -4294,19 +4282,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="Z4" s="1" t="n">
         <v>0.7419</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="1" t="n">
         <v>0.5152</v>
       </c>
-      <c r="AC4" s="2" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.6444</v>
       </c>
-      <c r="AD4" s="2" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.7838000000000001</v>
       </c>
     </row>
@@ -4334,10 +4322,10 @@
       <c r="E5" t="n">
         <v>62</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.4281</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -4350,10 +4338,10 @@
           <t>[0.587, 0.800]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -4366,10 +4354,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.2258</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.3807</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -4382,10 +4370,10 @@
           <t>[0.131, 0.321]</t>
         </is>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T5" t="inlineStr">
@@ -4398,10 +4386,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="W5" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X5" t="inlineStr">
@@ -4414,19 +4402,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="Z5" s="1" t="n">
         <v>0.6935</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="1" t="n">
         <v>0.4242</v>
       </c>
-      <c r="AC5" s="2" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.6042</v>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.7532</v>
       </c>
     </row>
@@ -4454,10 +4442,10 @@
       <c r="E6" t="n">
         <v>62</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="1" t="n">
         <v>0.4203</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -4470,10 +4458,10 @@
           <t>[0.605, 0.814]</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L6" t="inlineStr">
@@ -4486,10 +4474,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.2419</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.3919</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -4502,10 +4490,10 @@
           <t>[0.144, 0.339]</t>
         </is>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -4518,10 +4506,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X6" t="inlineStr">
@@ -4534,19 +4522,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="Z6" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="1" t="n">
         <v>0.4545</v>
       </c>
-      <c r="AC6" s="2" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.617</v>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.7632</v>
       </c>
     </row>
@@ -4574,10 +4562,10 @@
       <c r="E7" t="n">
         <v>62</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>0.6452</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.4448</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -4590,10 +4578,10 @@
           <t>[0.534, 0.756]</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="L7" t="inlineStr">
@@ -4606,10 +4594,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.1774</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.3369</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -4622,10 +4610,10 @@
           <t>[0.094, 0.261]</t>
         </is>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -4638,10 +4626,10 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.4677</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="W7" s="1" t="n">
         <v>0.503</v>
       </c>
       <c r="X7" t="inlineStr">
@@ -4654,19 +4642,19 @@
           <t>[0.343, 0.593]</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="Z7" s="1" t="n">
         <v>0.6452</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="1" t="n">
         <v>0.3333</v>
       </c>
-      <c r="AC7" s="2" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.5686</v>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.725</v>
       </c>
     </row>
